--- a/human_resources_forms/016_tech_company_employee_admission_form--human_resources_forms.xlsx
+++ b/human_resources_forms/016_tech_company_employee_admission_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'software_engineer',_'value':_'software_engineer'}</t>
+          <t>software_engineer</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Software Engineer', 'value': 'Software Engineer'}</t>
+          <t>Software Engineer</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'dev_manager',_'value':_'dev_manager'}</t>
+          <t>dev_manager</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Dev Manager', 'value': 'Dev Manager'}</t>
+          <t>Dev Manager</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'virtual',_'value':_'virtual'}</t>
+          <t>virtual</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Virtual', 'value': 'Virtual'}</t>
+          <t>Virtual</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'in-office',_'value':_'in-office'}</t>
+          <t>in-office</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'In-office', 'value': 'In-office'}</t>
+          <t>In-office</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'hr',_'value':_'hr'}</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'HR', 'value': 'HR'}</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'marketing',_'value':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Marketing', 'value': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_started',_'value':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not Started', 'value': 'Not Started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'In Progress', 'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'completed',_'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Completed', 'value': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
